--- a/AAII_Financials/Quarterly/IMO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IMO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>IMO</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11253400</v>
+      </c>
+      <c r="E8" s="3">
         <v>8894900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8205000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8610900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8217900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8672900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8720200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9782000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9752700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9045700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9996700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10255400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8883900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8911200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14400000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10983100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>12773400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>12657000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12295000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7565900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5790800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6992000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6017000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5937000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2876900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5231600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6332500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7202000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7318000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6131600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5975300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7046700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7177100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5965100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6010200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5323300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5213200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>5376100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>5640300</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>5122600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8823300</v>
+      </c>
+      <c r="E9" s="3">
         <v>7364600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7092700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7022100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6783000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6980900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7119600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8077300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8184000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7356100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8034000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8181900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7732200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7215800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10858000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8271400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9554400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10009000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9859000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5794800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4654600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5372000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4790000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5000000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2658700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4557200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5145000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5803400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5850100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4996100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4329800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5507600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6160100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4675600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4747300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4159400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>4589500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>4385100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>4315900</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>3931800</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2430100</v>
+      </c>
+      <c r="E10" s="3">
         <v>1530200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1112200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1588800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1434900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1692000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1600600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1704700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1568700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1689700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1962700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2073600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1151600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1695500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3542000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2711700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3219000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2648000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2436000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1771100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1136200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1620000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1227000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>937000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>218200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>674400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1187400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1398600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1467900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1135500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1645500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1539100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1017000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1289500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1262900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1163900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>623600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>991000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1324400</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1190800</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,19 +1248,20 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>97700</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1255,11 +1269,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>82000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1267,11 +1281,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>63600</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1279,86 +1293,89 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3">
         <v>1000</v>
-      </c>
-      <c r="R12" s="3">
-        <v>700</v>
       </c>
       <c r="S12" s="3">
         <v>700</v>
       </c>
       <c r="T12" s="3">
+        <v>700</v>
+      </c>
+      <c r="U12" s="3">
         <v>2000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>26000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>4000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>25400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>4600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>800</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>6000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>114600</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>5200</v>
       </c>
-      <c r="AM12" s="3" t="s">
+      <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>16900</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>14600</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,58 +1496,61 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-5700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-4400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>544200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-7000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-9000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-1500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-40900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-9800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1547,20 +1567,20 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1496000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-120000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>15700</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1577,8 +1597,8 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
@@ -1601,130 +1621,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>359800</v>
+      </c>
+      <c r="E15" s="3">
         <v>372500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>480600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>362600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>350500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>369400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>367700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>376000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>333200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>361900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>370300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>351100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>342100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>362200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>465000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>404500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>333300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>426000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>545000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>361500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>325400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>494000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>467000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>409000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>324100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>355600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>309500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>347400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>310900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>300200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>312000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>297900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>269500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>283800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>771700</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>291000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>262000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>301100</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>306500</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>305800</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9286700</v>
+      </c>
+      <c r="E17" s="3">
         <v>8025900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7765200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7612900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7321900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7535400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7664500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8619900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8680100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7901100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8595100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8723700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8245700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7730900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12148000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9257400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10441900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>11145000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>11179000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6695500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5469700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6472000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7478000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5942000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3441900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5437300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6030700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6766700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6747800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5816800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5156400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6304800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6965600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5430600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6144900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4944500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>5314400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>5164000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>5197800</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>4794500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1966800</v>
+      </c>
+      <c r="E18" s="3">
         <v>869000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>439800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>997900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>896000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1137500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1055700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1162100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1072600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1144700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1401600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1531700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>638100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1180300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2252000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1725700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2331500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1512000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1116000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>870400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>321100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>520000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1461000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-565000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-205700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>301700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>435300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>570200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>314900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>818900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>742000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>211500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>534500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-134700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>378800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-101200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>212000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>442500</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,19 +2085,20 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3">
         <v>-3600</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>8</v>
@@ -2096,574 +2130,589 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>53000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>111500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>15500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>29000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>14100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>28900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>5000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>13000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>18000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>34500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>20400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>40600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>26200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>13100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>27400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>25400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>7500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-5200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>3000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>20800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>118300</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>845800</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>596100</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2326600</v>
+      </c>
+      <c r="E21" s="3">
         <v>1241500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>924100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1360500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1246500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1506900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1423400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1538200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1405800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1506500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1771900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1882800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>980200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1542500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2770000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2241700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2680300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1967000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1664000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1245900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>675500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1019000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>550000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>422000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-206400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>170400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>608900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>823200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>907200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>628200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1158400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1031900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>487800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>825800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>631800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>672800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>181600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>631500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1594800</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1229900</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E22" s="3">
         <v>7900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>26000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>9400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>13000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>15000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>10000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>13300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>14900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>14800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>16600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>18200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>21600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>19800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>21800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>19600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>17300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>15600</v>
-      </c>
-      <c r="AL22" s="3">
-        <v>12700</v>
       </c>
       <c r="AM22" s="3">
         <v>12700</v>
       </c>
       <c r="AN22" s="3">
+        <v>12700</v>
+      </c>
+      <c r="AO22" s="3">
         <v>7700</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>10800</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2013900</v>
+      </c>
+      <c r="E23" s="3">
         <v>882600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>458700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>503300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>912100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1174400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1094600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1186600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1087900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1160900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1317600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1552400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>667600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1215800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2279000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1825500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2339600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1534000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1111000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>880700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>340600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>512000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1463000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-543800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-200200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>284600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>459300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>578100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>306400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>826500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>745600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>198700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>524700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-155500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>369100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-93000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>322700</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1277600</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>908000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>471800</v>
+      </c>
+      <c r="E24" s="3">
         <v>209200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>99900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>116300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>216300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>278300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>243300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>270900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>260100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>278400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>284000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>368900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>157800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>293400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>552000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>345400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>559400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>361000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>298000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>208100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>75900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>120000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-317000</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-131100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-52600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>73300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>107800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-383000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>80800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>177300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>201300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>51200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>136300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-53600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>93000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-35700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>66800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>168200</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>137500</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1542100</v>
+      </c>
+      <c r="E26" s="3">
         <v>673400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>358800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>387000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>695800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>896100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>851400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>915700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>827800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>882500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1033600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1183500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>509700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>922400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1727000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1480100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1780200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1173000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>813000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>672600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>264700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>392000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1146000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-412800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-147600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>211300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>351500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>961100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>225600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>649200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>544300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>147500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>388400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-102000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>276100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-57300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>255800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1109300</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>770500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1542100</v>
+      </c>
+      <c r="E27" s="3">
         <v>673400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>358800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>387000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>695800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>896100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>851400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>915700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>827800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>882500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1033600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1183500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>509700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>922400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1727000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1480100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1780200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1173000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>813000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>672600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>264700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>392000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1146000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-412800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-147600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>211300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>351500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>961100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>225600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>649200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>544300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>147500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>388400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-102000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>276100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-57300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>255800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1109300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>770500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,19 +3583,22 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3">
         <v>3600</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>8</v>
@@ -3560,208 +3630,214 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>-53000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-111500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-15500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-29000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-14100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-28900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-13000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-18000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-34500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-40600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-26200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-13100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-27400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-25400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-6800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-7500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>5200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-20800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-118300</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-845800</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-596100</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1542100</v>
+      </c>
+      <c r="E33" s="3">
         <v>673400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>358800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>387000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>695800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>896100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>851400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>915700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>827800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>882500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1033600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1183500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>509700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>922400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1727000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1480100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1780200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1173000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>813000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>672600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>264700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>392000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1146000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-412800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-147600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>211300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>351500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>961100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>225600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>649200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>544300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>147500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>388400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-102000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>276100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-57300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>255800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1109300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>770500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1542100</v>
+      </c>
+      <c r="E35" s="3">
         <v>673400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>358800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>387000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>695800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>896100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>851400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>915700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>827800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>882500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1033600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1183500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>509700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>922400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1727000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1480100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1780200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1173000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>813000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>672600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>264700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>392000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1146000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-412800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-147600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>211300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>351500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>961100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>225600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>649200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>544300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>147500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>388400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-102000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>276100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-57300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>255800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1109300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>770500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1999200</v>
+      </c>
+      <c r="E41" s="3">
         <v>737200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>832900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1336100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1749400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1227300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>680400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1102900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1475900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>868500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>654200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2007800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1794300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1657800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3749000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2606000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2118700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3149000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2153000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1388900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>561200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1467000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>771000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>817000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>182800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1089600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1339500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1269300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>862000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>778300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>752000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>834200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>657200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1072700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>889300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>619900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>463600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>516300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>300400</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>190500</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,252 +4553,261 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5754500</v>
+      </c>
+      <c r="E43" s="3">
         <v>5479800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3187900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3703100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4107500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4014300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4001800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4089000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4435000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3843100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3393800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3984500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3462500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3165500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4719000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3774200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5054000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5413000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3869000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2867400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2287500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2388000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1919000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1732000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1464300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1221500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2104300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2391000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2485300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2488800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1924800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1983100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1976100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1720100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2018300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1411000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1190000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1340600</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1554100</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1307500</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2065300</v>
+      </c>
+      <c r="E44" s="3">
         <v>2035300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2118000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2107800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1957700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1997400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1818800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1771300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2123300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2325500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2235300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1961900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1758800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2029500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2268000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1089500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1030200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1374000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1102000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1040700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>877300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1256000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1161000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1088000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>983300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>825100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1010500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>819900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>973800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>963000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>987100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1011600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>919200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>950000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>800000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>736000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>777000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>792800</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>729100</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>722900</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4751,517 +4850,529 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3">
         <v>550200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>583100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>782000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>689000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>540000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>522200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>737000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>673000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>764000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>581500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>543300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>480300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>502400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>500400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>437300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>411700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>337200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>343300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>342500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>316300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>328200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>364700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>351100</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>359500</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>420200</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9819000</v>
+      </c>
+      <c r="E46" s="3">
         <v>8252300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6138800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7147000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7814600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7239000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6501100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6963200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8034200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7037000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6283400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7954200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7015600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6852900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10736000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8020000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8785900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10718000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7813000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5837000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4248200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5848000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4524000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4401000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3211900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3679500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4934500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4982600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4821600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4667400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4075600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4166100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3895700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4085400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4023900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3095200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2795300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>3000700</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>2943100</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2641200</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>722500</v>
+      </c>
+      <c r="E47" s="3">
         <v>755100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>804500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>797600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>802100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>751400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>753400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>793500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>786200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>799000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>804200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>774700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>753700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>735400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>893000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>643500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>557200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>754000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>757000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>557800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>541000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>765000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>781000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>771000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>692100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>708100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>694700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>756100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>709000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>657400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>652300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>608200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>647400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>639900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>643700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>692900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>675000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>779000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>791300</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>940300</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21721000</v>
+      </c>
+      <c r="E48" s="3">
         <v>22081700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22717200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21699500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22486200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21338600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21577800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22817300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22535300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22774200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>23497100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22458700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>23016900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>22499500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>30506000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21872300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>22883600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>31107000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>31240000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>23242900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>22848700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>31700000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>32222000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>33582000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>26572100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>26751400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>26869800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>28614700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>27358400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>26581900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>26048300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>24857200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>25778500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>25859800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>25655200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>26490900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>26677000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>27704700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>27912100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>28226300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>116900</v>
+      </c>
+      <c r="E49" s="3">
         <v>118900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>121100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>119200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>121700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>115500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>115400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>122900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>121300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>122600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>125700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>122700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>125400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>122700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>166000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>121000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>122700</v>
-      </c>
-      <c r="T49" s="3">
-        <v>166000</v>
       </c>
       <c r="U49" s="3">
         <v>166000</v>
       </c>
       <c r="V49" s="3">
+        <v>166000</v>
+      </c>
+      <c r="W49" s="3">
         <v>123000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>120100</v>
-      </c>
-      <c r="X49" s="3">
-        <v>166000</v>
       </c>
       <c r="Y49" s="3">
         <v>166000</v>
@@ -5270,55 +5381,58 @@
         <v>166000</v>
       </c>
       <c r="AA49" s="3">
-        <v>130300</v>
+        <v>166000</v>
       </c>
       <c r="AB49" s="3">
         <v>130300</v>
       </c>
       <c r="AC49" s="3">
+        <v>130300</v>
+      </c>
+      <c r="AD49" s="3">
         <v>145000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>154200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>147500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>143200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>141600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>135200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>836300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>715900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>637000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>509000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>443500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>328000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>353400</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,107 +5678,110 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1324600</v>
+      </c>
+      <c r="E52" s="3">
         <v>1354700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1075800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1081200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1167300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1090200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>894500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>783900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>770100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>662400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>486100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>910000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>900900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>916500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1223000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>669700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>825500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1065000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>806000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>517000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>403600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>528000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>338000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>462000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>390800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>456900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>247900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>235500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>214100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>665100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>634000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>622800</v>
       </c>
-      <c r="AI52" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
@@ -5674,17 +5794,20 @@
       <c r="AM52" s="3">
         <v>0</v>
       </c>
-      <c r="AN52" s="3" t="s">
-        <v>8</v>
+      <c r="AN52" s="3">
+        <v>0</v>
       </c>
       <c r="AO52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AP52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ52" s="3">
         <v>341100</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>33704000</v>
+      </c>
+      <c r="E54" s="3">
         <v>32562700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>30857300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30844500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>32391900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30534700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29842100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>31480800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32247100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>31395300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>31196500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32220300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31812400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31126900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>43524000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>31326500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>33174700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>43810000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>40782000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>30277700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>28161500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>39007000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>38031000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>39382000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>30997200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>31726200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>32891900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>34743000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>33250500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>32715000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>31551700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>30389400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>31158000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>31301000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>30959900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>30788000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>30590800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>31812400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>31999900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>32337900</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6453100</v>
+      </c>
+      <c r="E57" s="3">
         <v>6265000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3087300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4509300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4587000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4573000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3395100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4420600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5319100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4869600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3533200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5136200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4257700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4176600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6094000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4668400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5809200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7269000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4667000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3995600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3120700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3629000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2712000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3134000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2409200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2445400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3220000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3113900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3036500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3498800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2806900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3317300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2953200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2605400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2560100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2263100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2204400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2291600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2148700</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>2226300</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E58" s="3">
         <v>68800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>77300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>81100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>88700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>80700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>82700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>159900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>160700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>146200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>157500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>168500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>172200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>164100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>122000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>88900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>90200</v>
-      </c>
-      <c r="T58" s="3">
-        <v>122000</v>
       </c>
       <c r="U58" s="3">
         <v>122000</v>
       </c>
       <c r="V58" s="3">
+        <v>122000</v>
+      </c>
+      <c r="W58" s="3">
         <v>90400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>142500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>191000</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>227000</v>
       </c>
       <c r="Z58" s="3">
         <v>227000</v>
       </c>
       <c r="AA58" s="3">
+        <v>227000</v>
+      </c>
+      <c r="AB58" s="3">
         <v>178900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>179800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>190200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>185700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>188700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>190100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>153700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>146800</v>
-      </c>
-      <c r="AI58" s="3">
-        <v>152100</v>
       </c>
       <c r="AJ58" s="3">
         <v>152100</v>
       </c>
       <c r="AK58" s="3">
-        <v>150300</v>
+        <v>152100</v>
       </c>
       <c r="AL58" s="3">
         <v>150300</v>
       </c>
       <c r="AM58" s="3">
+        <v>150300</v>
+      </c>
+      <c r="AN58" s="3">
         <v>151100</v>
-      </c>
-      <c r="AN58" s="3">
-        <v>155200</v>
       </c>
       <c r="AO58" s="3">
         <v>155200</v>
       </c>
       <c r="AP58" s="3">
+        <v>155200</v>
+      </c>
+      <c r="AQ58" s="3">
         <v>208200</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>576000</v>
+      </c>
+      <c r="E59" s="3">
         <v>318100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1328100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>221800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>213400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>202500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>985500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>196900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>227200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>186100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>917700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>394800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>226600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>459000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2682000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1753400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1554800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1260000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>765000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>320700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>99800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>113000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>441000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>95000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>83200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>95800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>172300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>130200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>115800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>123200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>49500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>67000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>55000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>367600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>43900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>29800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>18400</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>679100</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>347200</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7134000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6696900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4825300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4856100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4933800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4898600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4869900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4823300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5752400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5247700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4999900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5746100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4704000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4846200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8898000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6510700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7454200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8651000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5554000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4406700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3363000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3933000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3380000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3456000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2671300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2721000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3582600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3429800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3341000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3812100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3010100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3472100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3172300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2812400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3078100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2457400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2385200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2465300</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2983000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2781800</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2897000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2951600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3009900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2951400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3028200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2875400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2874500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3069000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3035100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3037400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3121200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3059700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3133200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3077600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4033000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2942700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3727500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5049000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5054000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3748100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3663100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4953000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4957000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4962000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3896200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3900900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3867900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4115400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3939700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3830600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3788700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3623300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3757900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3763200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3724800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3730700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3735200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3861100</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3865700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>5407600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2811100</v>
+      </c>
+      <c r="E62" s="3">
         <v>2960900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2916600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2303800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2145400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2015500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2001600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2142200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2088200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2083300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2109600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1821500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1824500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1771600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8180000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5615800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5750800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7834000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8439000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6412600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6114800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>8385000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8276000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>8172000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6446600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6600700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6514100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6500600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6126900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6351000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6114600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5868700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>6337700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>6218800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>5972300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>5979000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>5865100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>6046700</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>5929200</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>5724800</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16421400</v>
+      </c>
+      <c r="E66" s="3">
         <v>16266000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14626700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13841000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14062300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13551300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13528300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13982800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14758300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14327400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14369700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14620600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13818200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13806300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>21111000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15069300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16932500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>21534000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>19047000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14567400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13140900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17271000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16613000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16590000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13014100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13222600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13964700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>14045800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13407600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13993800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>12913400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>12964100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13267900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>12794400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>12775100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>12167100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>11985500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>12373100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>12778000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>13914200</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16662200</v>
+      </c>
+      <c r="E72" s="3">
         <v>15683500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15588000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16478000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17779700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16465000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15807900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>17250800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17237400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16823500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16588300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17167300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17535100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16878700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>21846000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>16228800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>16193500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>22171000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>21660000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>16117800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15430600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>22281000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>22050000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>23358000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18453900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>19001400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>19345200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>20718000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19869900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>18755900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>18692400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>17620100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>18103800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>18715100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>18392400</v>
-      </c>
-      <c r="AL72" s="3">
-        <v>18772000</v>
       </c>
       <c r="AM72" s="3">
         <v>18772000</v>
       </c>
       <c r="AN72" s="3">
+        <v>18772000</v>
+      </c>
+      <c r="AO72" s="3">
         <v>19634400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>19476200</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>18465200</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17282600</v>
+      </c>
+      <c r="E76" s="3">
         <v>16296800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16230500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17003500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18329600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16983300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16313800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17498100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17488800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17067900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16826800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17599700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17994300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17320600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>22413000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16257200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16242300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>22276000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>21735000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15710400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15020600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>21736000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>21418000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>22792000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17983100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>18503600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>18927300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>20697200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>19842900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>18721300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>18638300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>17425300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>17890100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>18506600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>18184800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>18620900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>18605300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>19439300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>19221900</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>18423700</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1542100</v>
+      </c>
+      <c r="E81" s="3">
         <v>673400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>358800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>387000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>695800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>896100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>851400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>915700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>827800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>882500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1033600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1183500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>509700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>922400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1727000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1480100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1780200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1173000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>813000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>672600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>264700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>392000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1146000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-412800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-147600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>211300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>351500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>961100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>225600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>649200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>544300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>147500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>388400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-102000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>276100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-57300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>255800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1109300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>770500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>350500</v>
+      </c>
+      <c r="E83" s="3">
         <v>369400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>367700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>376000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>333200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>361900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>370300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>351100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>342100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>362200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>343600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>404200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>350100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>341200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>465000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>404500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>333300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>426000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>545000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>361500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>325400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>494000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1998000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>409000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>324100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>355600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>309500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>347400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>310900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>300200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>312000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>264500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>269500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>283800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>771700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>291000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>262000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>301100</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>306500</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>305800</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1904100</v>
+      </c>
+      <c r="E89" s="3">
         <v>541600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1398900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1290800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1074200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1062400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1243400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1100700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1190200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>794600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>992700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1743900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>668300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-606800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2797000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2251100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1982000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1914000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1632000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1442200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>616200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1045000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>316000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>875000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-640300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>332100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>798400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1140800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>813600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>772100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>662900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>877100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>646600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>741500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>803700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>622900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>366200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>272000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>576900</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>593100</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-373200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-340300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-460900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-361800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-345300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-276900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-294000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-359700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-336800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-367000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-355900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-286100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-376800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-317100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-492000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-397000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-333000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-304000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-424000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-276000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-174300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-167000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-211000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-142000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-160900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-243400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-307200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-345700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-312400</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-331800</v>
       </c>
       <c r="AG91" s="3">
         <v>-331800</v>
       </c>
       <c r="AH91" s="3">
+        <v>-331800</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-237600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-268700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-279300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-230700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-179400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-238100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-93700</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-138300</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-145200</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-331000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-322400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-409200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-346000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-346100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-262300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-280800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-358300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-333200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-355200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-311200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-280900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-369300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-306000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-473000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>265300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-170000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-279000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-399000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-191900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-149700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-147000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-197000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-125000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-135000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-241800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-311100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-342400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-340200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-356400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-352400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-255800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-285300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-274800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-243400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-174100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-209100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>46900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>1226900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>772100</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>296500</v>
+      </c>
+      <c r="E96" s="3">
         <v>250700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>263300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>262800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>269100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>213600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>220300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>238400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>234500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>205300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>218100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>215900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>194100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>196600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-211000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-165400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-168500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-185000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-188000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-144400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-116400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-162000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-161000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-162000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-127100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-128700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-129400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-140100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-116600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-114700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-114900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-112600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-99400</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-100900</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-99700</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-101200</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-94500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-97600</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-98300</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-97600</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-298600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1514100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1321700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-272000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-253900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1317700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1134800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-240400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-209000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2083900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1211600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-198600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-200300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2151000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1999700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2020400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-639000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-955000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-436300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-966200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-202000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-165000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-166000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-131100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-349300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-341500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-430300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-413200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-398000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-432300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-421500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-776900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-293600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-291000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-292500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-193500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-102900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1693900</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-1324400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1274600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-81000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-524400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-376900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>456100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>546100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-355100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-392300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>616700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>230400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1402400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>251300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>100400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1113100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>173000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>516700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-208400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>996000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>278000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>814100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-499700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>696000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-46000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>584000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-906400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-259100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>145800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>368100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>60300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>17700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-121800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>199800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-415500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>173100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>269400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>156300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-36500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>215900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>109900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>40700</v>
       </c>
     </row>
